--- a/task196/golden/member_incidence_review.xlsx
+++ b/task196/golden/member_incidence_review.xlsx
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>22301200</v>
+        <v>22233300</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>400</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F2" t="n">
         <v>31</v>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -819,13 +819,13 @@
         <v>311088</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>272896</v>
+        <v>271791</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>81499</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>665484</v>
+        <v>664379</v>
       </c>
     </row>
     <row r="3">
@@ -838,13 +838,13 @@
         <v>309882</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>230899</v>
+        <v>228966</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>83191</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>623972</v>
+        <v>622039</v>
       </c>
     </row>
     <row r="4">
@@ -857,13 +857,13 @@
         <v>317029</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>220954</v>
+        <v>222673</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>75171</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>613153</v>
+        <v>614872</v>
       </c>
     </row>
     <row r="5">
@@ -876,13 +876,13 @@
         <v>339633</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>182147</v>
+        <v>181104</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>75823</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>597604</v>
+        <v>596560</v>
       </c>
     </row>
   </sheetData>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>322554</v>
+        <v>307226</v>
       </c>
     </row>
     <row r="3">
@@ -1126,13 +1126,13 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="3">
@@ -1142,13 +1142,13 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>12.9</v>
+        <v>15.1</v>
       </c>
       <c r="C3" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D3" s="4" t="n">
         <v>3.8</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>5.8</v>
+        <v>8.5</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>7.4</v>
+        <v>2.5</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.9</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="5">
@@ -1174,13 +1174,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5.1</v>
+        <v>2.5</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>3.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2.3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/task196/golden/member_incidence_review.xlsx
+++ b/task196/golden/member_incidence_review.xlsx
@@ -670,7 +670,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>cases</t>
+          <t>cases_per_million_payments</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -682,26 +682,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cases Castlegate's own register holds</t>
+          <t>Incidence its own register holds</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>400</v>
+        <v>18</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>scam cases notified in the scheme year to 31 March 2027</t>
+          <t>scam cases notified in the scheme year to 31 March 2027, per million payments sent</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cases its own record did not hold</t>
+          <t>Incidence its own record did not hold</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>288</v>
+        <v>13</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -712,15 +712,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Indexed cases</t>
+          <t>Indexed incidence</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>688</v>
+        <v>31</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cases its customers suffered in the year, recorded or not</t>
+          <t>cases its customers suffered in the year, recorded or not, per million payments sent</t>
         </is>
       </c>
     </row>
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>311088</v>
+        <v>389667</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>271791</v>
+        <v>390380</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>81499</v>
+        <v>204473</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>664379</v>
+        <v>984521</v>
       </c>
     </row>
     <row r="3">
@@ -835,16 +835,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>309882</v>
+        <v>349939</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>228966</v>
+        <v>277918</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>83191</v>
+        <v>101820</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>622039</v>
+        <v>729677</v>
       </c>
     </row>
     <row r="4">
@@ -854,16 +854,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>317029</v>
+        <v>343190</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>222673</v>
+        <v>237744</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>75171</v>
+        <v>92670</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>614872</v>
+        <v>673605</v>
       </c>
     </row>
     <row r="5">

--- a/task196/golden/member_incidence_review.xlsx
+++ b/task196/golden/member_incidence_review.xlsx
@@ -772,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -883,6 +883,13 @@
       </c>
       <c r="E5" s="2" t="n">
         <v>596560</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Unauthorised fraud, settled by advice, each case in the quarter it closed. Quarter totals are taken from the tier amounts before rounding.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/task196/golden/member_incidence_review.xlsx
+++ b/task196/golden/member_incidence_review.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -639,7 +639,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Index set for the indemnity year beginning 1 October 2027, on the scheme year ended 31 March 2027, to the nearest whole case per million payments sent.</t>
+          <t>Index set for the indemnity year beginning 1 October 2027, on the scheme year ended 31 March 2027, to the nearest case per million payments sent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cases indexed are the two-source estimate of the cases the member recorded against the register sightings no fund-return request of its own preceded, 400 x 270 / 157 = 688 for Castlegate. The count moves with the form of the estimate while the index does not, so a count is read inside 686 to 689 (Castlegate, 286 to 289 for the cases its record did not hold), 138 to 139 (Saltmarch), 300 to 302 (Trentmoor) and 516 to 517 (Brindlemere).</t>
         </is>
       </c>
     </row>
@@ -903,7 +910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1082,6 +1089,13 @@
       </c>
       <c r="C13" s="2" t="n">
         <v>153760</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Distinct cases notified in the 2027/28 first quarter, 1 April to 30 June 2027, counted once each from the notification feed's main extract and its quarter-end supplement together, with the value the member reported on them.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1095,7 +1109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1204,6 +1218,13 @@
       </c>
       <c r="D6" s="4" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Scam reimbursement cases from 2025/26 payments, by the quarter of that year each case closed in. The recovery is every case-level credit on those cases by route and the reimbursement is what the register holds for them, so the year line covers the same four quarters as the rows. Not the recovery statement, which counts a recovery in the quarter the money arrived and states repatriation net of the agent's charge.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1276,7 +1297,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Clause 4.4: the index is stated to the nearest whole case per million payments sent. Indemnity and reported value are stated to the nearest pound and recovery shares to one decimal place.</t>
+          <t>Clause 4.4: the index is stated to the nearest whole case per million payments sent, and the walk lines with it. Indemnity and reported value are stated to the pound and recovery shares to one decimal place.</t>
         </is>
       </c>
     </row>

--- a/task196/golden/member_incidence_review.xlsx
+++ b/task196/golden/member_incidence_review.xlsx
@@ -646,7 +646,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cases indexed are the two-source estimate of the cases the member recorded against the register sightings no fund-return request of its own preceded, 400 x 270 / 157 = 688 for Castlegate. The count moves with the form of the estimate while the index does not, so a count is read inside 686 to 689 (Castlegate, 286 to 289 for the cases its record did not hold), 138 to 139 (Saltmarch), 300 to 302 (Trentmoor) and 516 to 517 (Brindlemere).</t>
+          <t>Cases indexed are the two-source estimate of the cases the member recorded against the register sightings no fund-return request of its own preceded, 400 x 270 / 157 = 688 for Castlegate. The count moves with the form of the estimate while the index does not, so a count is read inside 686 to 689 (Castlegate, 286 to 289 for the cases its record did not hold), 138 to 140 (Saltmarch), 300 to 302 (Trentmoor) and 515 to 521 (Brindlemere).</t>
         </is>
       </c>
     </row>
